--- a/WorkBot/refactor-experimental/data/orders/SANICO/SANICO_Triphammer_20251027.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/SANICO/SANICO_Triphammer_20251027.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,12 +446,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EX0440041</t>
+          <t>EX0070041</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Machine Detergent - Extreme AllTemp Machine Detergent</t>
+          <t>Manual Dish Detergent - Extreme Blue Ultra Pot &amp; Pan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -461,24 +461,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>68.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>174.24</t>
+          <t>137.58</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EX0070041</t>
+          <t>41SANIT10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Manual Dish Detergent - Extreme Blue Ultra Pot &amp; Pan</t>
+          <t>Sanitizer - Sani-T-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -488,64 +488,10 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>68.79</t>
+          <t>108.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>137.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>EX0470041</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Machine Rinse Aid - Extreme AllTemp Rinse</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>107.82</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>215.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>41SANIT10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sanitizer - Sani-T-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>108.38</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>216.76</t>
         </is>
